--- a/data/trans_dic/P1414-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1414-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,78</t>
+          <t>1,38; 5,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,99</t>
+          <t>2,33; 6,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,05</t>
+          <t>2,66; 5,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,78</t>
+          <t>0,85; 2,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,04</t>
+          <t>1,34; 3,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,13</t>
+          <t>1,44; 3,11</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -808,27 +808,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,73</t>
+          <t>1,59; 4,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,27</t>
+          <t>2,54; 5,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,31</t>
+          <t>0,72; 2,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,46</t>
+          <t>0,94; 2,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,7</t>
+          <t>1,27; 2,58</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -908,37 +908,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,32</t>
+          <t>0,57; 3,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,19</t>
+          <t>0,5; 3,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,59</t>
+          <t>0,69; 2,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,74</t>
+          <t>0,29; 1,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,61</t>
+          <t>0,26; 1,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,52</t>
+          <t>0,44; 1,72</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,43</t>
+          <t>0,16; 3,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,75</t>
+          <t>1,32; 4,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,37</t>
+          <t>1,07; 4,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,02</t>
+          <t>1,35; 3,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,59</t>
+          <t>0,87; 2,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,32</t>
+          <t>0,62; 2,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,71</t>
+          <t>0,99; 2,71</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -1123,42 +1123,42 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,6</t>
+          <t>1,26; 6,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 9,58</t>
+          <t>3,63; 9,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,69</t>
+          <t>3,62; 7,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,37</t>
+          <t>0,63; 3,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,93</t>
+          <t>1,91; 5,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,34</t>
+          <t>2,05; 4,21</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -1238,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,01</t>
+          <t>0,17; 1,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,88</t>
+          <t>0,36; 2,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,72</t>
+          <t>0,77; 4,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,34</t>
+          <t>2,16; 5,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,46</t>
+          <t>0,18; 1,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,48</t>
+          <t>0,43; 2,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,13</t>
+          <t>1,2; 2,96</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1348,37 +1348,37 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,67</t>
+          <t>0,24; 1,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,71</t>
+          <t>0,61; 2,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,05</t>
+          <t>0,95; 3,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,2</t>
+          <t>3,61; 6,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,52</t>
+          <t>0,5; 1,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,65</t>
+          <t>0,56; 1,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,24</t>
+          <t>2,17; 3,54</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,91</t>
+          <t>0,28; 1,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,09</t>
+          <t>3,11; 6,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,25</t>
+          <t>4,75; 8,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,85</t>
+          <t>4,99; 7,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,34</t>
+          <t>1,67; 3,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,83</t>
+          <t>2,72; 4,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,69</t>
+          <t>2,63; 4,18</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1563,42 +1563,42 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,74</t>
+          <t>0,23; 0,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,72</t>
+          <t>0,25; 0,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,19</t>
+          <t>2,1; 3,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,19</t>
+          <t>2,95; 4,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,08; 4,43</t>
+          <t>3,69; 4,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,75</t>
+          <t>1,16; 1,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,38</t>
+          <t>1,7; 2,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,49</t>
+          <t>2,06; 2,62</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12138</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>13506</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4833</t>
+          <t>0; 5285</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6556</t>
+          <t>0; 7055</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4002</t>
+          <t>0; 3213</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4086; 16589</t>
+          <t>3971; 16098</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6030; 20187</t>
+          <t>6725; 19590</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7830; 17510</t>
+          <t>8396; 18219</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4950; 16195</t>
+          <t>4972; 16594</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8262; 23552</t>
+          <t>7777; 22915</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8302; 18794</t>
+          <t>9140; 19754</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19627</t>
+          <t>19961</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19627</t>
+          <t>19961</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5217</t>
+          <t>0; 5200</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5907</t>
+          <t>0; 5368</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,32 +2039,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6464; 21952</t>
+          <t>6462; 21939</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8956; 24755</t>
+          <t>8314; 24173</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13895; 26870</t>
+          <t>13737; 28483</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7267; 23810</t>
+          <t>7430; 23346</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8921; 25267</t>
+          <t>9628; 25192</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13461; 27788</t>
+          <t>13594; 27680</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>6212</t>
         </is>
       </c>
     </row>
@@ -2197,37 +2197,37 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5033</t>
+          <t>0; 4812</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1947; 11311</t>
+          <t>1950; 11114</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1870; 10724</t>
+          <t>1682; 10143</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2263; 9027</t>
+          <t>2465; 10150</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1951; 11559</t>
+          <t>1946; 11016</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1704; 10545</t>
+          <t>1727; 10229</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2617; 10115</t>
+          <t>2972; 11543</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>12967</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6297</t>
+          <t>0; 5780</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4808</t>
+          <t>0; 4867</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>585; 10687</t>
+          <t>600; 13076</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5849; 18494</t>
+          <t>5117; 18357</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4185; 16934</t>
+          <t>4160; 16949</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4206; 14371</t>
+          <t>5678; 14867</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6741; 19758</t>
+          <t>6670; 20311</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4148; 17601</t>
+          <t>4691; 17119</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7282; 21330</t>
+          <t>7885; 21553</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11930</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11972</t>
+          <t>12451</t>
         </is>
       </c>
     </row>
@@ -2518,42 +2518,42 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 6861</t>
+          <t>0; 6774</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2678</t>
+          <t>0; 2745</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2991; 14487</t>
+          <t>2767; 14585</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7237; 20948</t>
+          <t>7931; 21329</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7791; 15944</t>
+          <t>8168; 16832</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2624; 14570</t>
+          <t>2730; 13681</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9296; 25483</t>
+          <t>8196; 24576</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8416; 16752</t>
+          <t>8834; 18125</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10560</t>
+          <t>10595</t>
         </is>
       </c>
     </row>
@@ -2686,37 +2686,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>468; 5429</t>
+          <t>452; 5273</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>988; 7996</t>
+          <t>990; 8125</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2223; 12897</t>
+          <t>2100; 12529</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5271; 13670</t>
+          <t>5665; 14118</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>992; 8035</t>
+          <t>996; 8575</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3041; 13300</t>
+          <t>2312; 13112</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6617; 16434</t>
+          <t>6414; 15800</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29912</t>
+          <t>35887</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>34727</t>
+          <t>40979</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 7389</t>
+          <t>0; 7248</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2849,37 +2849,37 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1780; 10326</t>
+          <t>1737; 10975</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4909; 18778</t>
+          <t>4258; 18040</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6479; 21116</t>
+          <t>6561; 21873</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13686; 43910</t>
+          <t>27575; 46187</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6118; 20643</t>
+          <t>6837; 21982</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6642; 22248</t>
+          <t>7481; 22721</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21316; 47427</t>
+          <t>32103; 52399</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44311</t>
+          <t>50919</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>46288</t>
+          <t>53038</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 7434</t>
+          <t>0; 7623</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2596; 14869</t>
+          <t>2150; 14272</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 8077</t>
+          <t>0; 7245</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25438; 50058</t>
+          <t>25535; 50674</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>38918; 68131</t>
+          <t>39219; 67942</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>34738; 55974</t>
+          <t>41280; 64026</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26886; 53502</t>
+          <t>26791; 50638</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>45617; 77461</t>
+          <t>43670; 75577</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>28023; 60613</t>
+          <t>42830; 67963</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>139611</t>
+          <t>154942</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>153915</t>
+          <t>169709</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3156; 14751</t>
+          <t>3101; 14843</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7736; 24968</t>
+          <t>7964; 23343</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8274; 24721</t>
+          <t>8751; 24926</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>74465; 113465</t>
+          <t>74492; 112317</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>103445; 148355</t>
+          <t>104683; 152413</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>112384; 161418</t>
+          <t>137214; 175174</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>81633; 122298</t>
+          <t>80983; 122212</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>117704; 165178</t>
+          <t>118219; 163638</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>129157; 176545</t>
+          <t>149484; 190076</t>
         </is>
       </c>
     </row>
